--- a/data/trans_orig/IP05B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05B-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29160</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53348</t>
+          <t>53978</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45344</t>
+          <t>46005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>61074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96197</t>
+          <t>96436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116192</t>
+          <t>116305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35834</t>
+          <t>35372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>76883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104083</t>
+          <t>103177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87200</t>
+          <t>87356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115872</t>
+          <t>115619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>169454</t>
+          <t>172312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>210709</t>
+          <t>210666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249220</t>
+          <t>247852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280130</t>
+          <t>279383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>293729</t>
+          <t>293942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326956</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>551889</t>
+          <t>552055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>597957</t>
+          <t>598891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>57563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82883</t>
+          <t>83091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112040</t>
+          <t>110807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55594</t>
+          <t>57206</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79203</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>103458</t>
+          <t>103643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123495</t>
+          <t>124219</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>88951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108763</t>
+          <t>108403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198465</t>
+          <t>197003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226790</t>
+          <t>226366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163121</t>
+          <t>164779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139514</t>
+          <t>140654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174620</t>
+          <t>174735</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278625</t>
+          <t>280302</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327664</t>
+          <t>326919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>411640</t>
+          <t>410425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>452777</t>
+          <t>452197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>442782</t>
+          <t>442604</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>482912</t>
+          <t>484571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>866177</t>
+          <t>866618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>926924</t>
+          <t>923325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63982</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66409</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92249</t>
+          <t>93414</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>135591</t>
+          <t>137050</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173342</t>
+          <t>175205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27825</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53622</t>
+          <t>53576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>68435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49370</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>107530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127611</t>
+          <t>128109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53404</t>
+          <t>52566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>73204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105139</t>
+          <t>108532</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140724</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>318444</t>
+          <t>319102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>349164</t>
+          <t>350600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>349104</t>
+          <t>349100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380708</t>
+          <t>380687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>675132</t>
+          <t>679062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>723110</t>
+          <t>720191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58267</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>73852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93582</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127469</t>
+          <t>124881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17010</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>37626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60310</t>
+          <t>58639</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>106722</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125642</t>
+          <t>125390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113330</t>
+          <t>114186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133244</t>
+          <t>133478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225066</t>
+          <t>225553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>254463</t>
+          <t>253165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>51156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>91233</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85499</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116176</t>
+          <t>116421</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>187203</t>
+          <t>186494</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>232470</t>
+          <t>229757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>493658</t>
+          <t>494033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>531448</t>
+          <t>533298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>528774</t>
+          <t>526978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>566872</t>
+          <t>568825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1029347</t>
+          <t>1029590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1086183</t>
+          <t>1085529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93435</t>
+          <t>91657</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>75333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105169</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146771</t>
+          <t>149285</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188578</t>
+          <t>188861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70115</t>
+          <t>70713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88747</t>
+          <t>88757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36258</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71912</t>
+          <t>71719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>47957</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72453</t>
+          <t>71964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>101184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136405</t>
+          <t>135806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>255344</t>
+          <t>256274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>287513</t>
+          <t>290216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287602</t>
+          <t>288560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>323669</t>
+          <t>324499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>556966</t>
+          <t>556132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>603281</t>
+          <t>604967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109723</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140607</t>
+          <t>140753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>101230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133516</t>
+          <t>133014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219006</t>
+          <t>220558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262232</t>
+          <t>263692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107764</t>
+          <t>107228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>126892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107919</t>
+          <t>107746</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129069</t>
+          <t>128648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>222433</t>
+          <t>222188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251609</t>
+          <t>250688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42854</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37122</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55444</t>
+          <t>56882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>68453</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93104</t>
+          <t>93611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,47 +8747,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>11355</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103261</t>
+          <t>104643</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>154914</t>
+          <t>155146</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196224</t>
+          <t>196394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>407538</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>449317</t>
+          <t>448179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>444786</t>
+          <t>444823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>487632</t>
+          <t>486019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>866538</t>
+          <t>862887</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>923895</t>
+          <t>925337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153802</t>
+          <t>151254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189987</t>
+          <t>189226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160275</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>196552</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>322510</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>375675</t>
+          <t>374741</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34292</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50047</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75937</t>
+          <t>75407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93206</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128745</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>178585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41432</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37189</t>
+          <t>35339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43649</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69446</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>243618</t>
+          <t>254352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>343068</t>
+          <t>343004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>378775</t>
+          <t>378689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>417259</t>
+          <t>417704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>632938</t>
+          <t>642606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>747889</t>
+          <t>748992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>65730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100669</t>
+          <t>99545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71429</t>
+          <t>73394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107332</t>
+          <t>109864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147578</t>
+          <t>147621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195959</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37357</t>
+          <t>37266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>91340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>110051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119514</t>
+          <t>119661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142073</t>
+          <t>141766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>217610</t>
+          <t>217315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247588</t>
+          <t>247921</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46853</t>
+          <t>46449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52255</t>
+          <t>52529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78746</t>
+          <t>78726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111418</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>154358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66196</t>
+          <t>64892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>78341</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110892</t>
+          <t>109560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>398807</t>
+          <t>398137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>483923</t>
+          <t>484972</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>551129</t>
+          <t>551811</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>596911</t>
+          <t>598862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>968693</t>
+          <t>964230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1066038</t>
+          <t>1069136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>102860</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143453</t>
+          <t>141829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115272</t>
+          <t>116583</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158708</t>
+          <t>159472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232477</t>
+          <t>231974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288061</t>
+          <t>291136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
